--- a/src/main/resources/customers.xlsx
+++ b/src/main/resources/customers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sicoob-my.sharepoint.com/personal/kelson_menezes_fornecedores_sicoob_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelsonthony/Documents/projects/batch-processing/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0620E63C-6043-439D-BFEF-E678404F5104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AE43F2-FF38-1D45-90D5-2EFAD468F772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6765" yWindow="1500" windowWidth="28800" windowHeight="11385" xr2:uid="{EF712562-E35D-480D-985A-DDB7617791B3}"/>
+    <workbookView xWindow="7340" yWindow="2040" windowWidth="28800" windowHeight="11380" xr2:uid="{EF712562-E35D-480D-985A-DDB7617791B3}"/>
   </bookViews>
   <sheets>
     <sheet name="customers" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="DadosExternos_1" localSheetId="0" hidden="1">'customers'!$A$1:$I$16</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
   <si>
     <t>id</t>
   </si>
@@ -92,9 +91,6 @@
   </si>
   <si>
     <t>Ukraine</t>
-  </si>
-  <si>
-    <t>3dfasdfsadfsd</t>
   </si>
   <si>
     <t>Jolyn</t>
@@ -335,12 +331,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -366,8 +369,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,20 +767,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC7386FE-58BF-4828-B6A7-4D1758F2BF4B}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -806,439 +809,439 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>41084</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1">
+        <v>37882</v>
+      </c>
+      <c r="I3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2">
-        <v>37882</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1">
+        <v>34466</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2">
-        <v>34466</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1">
+        <v>36989</v>
+      </c>
+      <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="2">
-        <v>36989</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1">
+        <v>33896</v>
+      </c>
+      <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="2">
-        <v>33896</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1">
+        <v>33017</v>
+      </c>
+      <c r="I7" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="2">
-        <v>33017</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1">
+        <v>43922</v>
+      </c>
+      <c r="I8" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="2">
-        <v>43922</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1">
+        <v>34098</v>
+      </c>
+      <c r="I9" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="2">
-        <v>34098</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="1">
+        <v>40475</v>
+      </c>
+      <c r="I10" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="2">
-        <v>40475</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1">
+        <v>36376</v>
+      </c>
+      <c r="I11" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2">
-        <v>36376</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="2">
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="1">
         <v>36382</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>39984</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="1">
+        <v>41229</v>
+      </c>
+      <c r="I14" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="2">
-        <v>41229</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="2">
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="1">
         <v>33205</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="1">
+        <v>42686</v>
+      </c>
+      <c r="I16" t="s">
         <v>92</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="2">
-        <v>42686</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/customers.xlsx
+++ b/src/main/resources/customers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelsonthony/Documents/projects/batch-processing/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AE43F2-FF38-1D45-90D5-2EFAD468F772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC5FBD-633F-9441-AA2A-51A51DE36F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7340" yWindow="2040" windowWidth="28800" windowHeight="11380" xr2:uid="{EF712562-E35D-480D-985A-DDB7617791B3}"/>
   </bookViews>
@@ -375,15 +375,20 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -435,15 +440,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{54020114-AFD4-41D8-B7AD-9069C986508C}" name="customers" displayName="customers" ref="A1:I16" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:I16" xr:uid="{54020114-AFD4-41D8-B7AD-9069C986508C}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{0BF554D3-6CD6-41EE-A194-72EF380408DA}" uniqueName="1" name="id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{06399C04-EFCB-4744-B849-301A3FFE6D00}" uniqueName="2" name="firstName" queryTableFieldId="2" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{717C29CB-C5EE-4AF4-AA28-BA36876B9A73}" uniqueName="3" name="lastName" queryTableFieldId="3" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{3C5CE79F-4D6A-40F7-94D1-F65D79571F3B}" uniqueName="4" name="email" queryTableFieldId="4" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{ECDFE398-6E7A-4417-9420-9FBDDF28F522}" uniqueName="5" name="gender" queryTableFieldId="5" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{566BFE86-DAE7-4895-96B0-DABE2CBAED51}" uniqueName="6" name="contactNo" queryTableFieldId="6" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{FDC0A6BD-D85A-4C2D-93FF-F6755EF35233}" uniqueName="7" name="country" queryTableFieldId="7" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{986E2FE6-A42D-48C3-93A2-9DB5F3C67094}" uniqueName="8" name="dob" queryTableFieldId="8" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{9775E88B-9F78-4882-A0EA-E3AFAE4AAD7D}" uniqueName="9" name="age" queryTableFieldId="9" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{0BF554D3-6CD6-41EE-A194-72EF380408DA}" uniqueName="1" name="id" queryTableFieldId="1" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{06399C04-EFCB-4744-B849-301A3FFE6D00}" uniqueName="2" name="firstName" queryTableFieldId="2" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{717C29CB-C5EE-4AF4-AA28-BA36876B9A73}" uniqueName="3" name="lastName" queryTableFieldId="3" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{3C5CE79F-4D6A-40F7-94D1-F65D79571F3B}" uniqueName="4" name="email" queryTableFieldId="4" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{ECDFE398-6E7A-4417-9420-9FBDDF28F522}" uniqueName="5" name="gender" queryTableFieldId="5" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{566BFE86-DAE7-4895-96B0-DABE2CBAED51}" uniqueName="6" name="contactNo" queryTableFieldId="6" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{FDC0A6BD-D85A-4C2D-93FF-F6755EF35233}" uniqueName="7" name="country" queryTableFieldId="7" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{986E2FE6-A42D-48C3-93A2-9DB5F3C67094}" uniqueName="8" name="dob" queryTableFieldId="8" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{9775E88B-9F78-4882-A0EA-E3AFAE4AAD7D}" uniqueName="9" name="age" queryTableFieldId="9" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -810,9 +815,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -839,9 +842,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
+      <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>15</v>
       </c>
@@ -868,9 +869,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
+      <c r="A4" s="2"/>
       <c r="B4" t="s">
         <v>22</v>
       </c>
@@ -897,9 +896,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
+      <c r="A5" s="2"/>
       <c r="B5" t="s">
         <v>29</v>
       </c>
@@ -926,9 +923,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
+      <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>35</v>
       </c>
@@ -955,9 +950,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
+      <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>41</v>
       </c>
@@ -984,9 +977,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
+      <c r="A8" s="2"/>
       <c r="B8" t="s">
         <v>47</v>
       </c>
@@ -1013,9 +1004,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
+      <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>53</v>
       </c>
@@ -1042,9 +1031,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
+      <c r="A10" s="2"/>
       <c r="B10" t="s">
         <v>60</v>
       </c>
@@ -1071,9 +1058,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
+      <c r="A11" s="2"/>
       <c r="B11" t="s">
         <v>65</v>
       </c>
@@ -1100,9 +1085,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>71</v>
       </c>
@@ -1129,9 +1112,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
+      <c r="A13" s="2"/>
       <c r="B13" t="s">
         <v>75</v>
       </c>
@@ -1158,9 +1139,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
+      <c r="A14" s="2"/>
       <c r="B14" t="s">
         <v>79</v>
       </c>
@@ -1187,9 +1166,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1216,9 +1193,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>88</v>
       </c>
